--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6A19C2-775B-4B86-A162-9338EC2D89DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C40D998-A502-49D8-880E-0F22E1D9E7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$230</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -410,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
@@ -1082,7 +1085,7 @@
         <v>36</v>
       </c>
       <c r="D40">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1422,7 +1425,7 @@
         <v>20</v>
       </c>
       <c r="D60">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1932,7 +1935,7 @@
         <v>30</v>
       </c>
       <c r="D90">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -2612,7 +2615,7 @@
         <v>30</v>
       </c>
       <c r="D130">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -2629,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -2646,7 +2649,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -2663,7 +2666,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -2680,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -2697,7 +2700,7 @@
         <v>5</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -2714,7 +2717,7 @@
         <v>6</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -2731,7 +2734,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -2748,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="D138">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -2765,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -2782,1539 +2785,9 @@
         <v>10</v>
       </c>
       <c r="D140">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>990011</v>
-      </c>
-      <c r="B141">
-        <v>99</v>
-      </c>
-      <c r="C141">
-        <v>11</v>
-      </c>
-      <c r="D141">
-        <v>200</v>
-      </c>
-      <c r="E141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>990012</v>
-      </c>
-      <c r="B142">
-        <v>99</v>
-      </c>
-      <c r="C142">
-        <v>12</v>
-      </c>
-      <c r="D142">
-        <v>300</v>
-      </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>990013</v>
-      </c>
-      <c r="B143">
-        <v>99</v>
-      </c>
-      <c r="C143">
-        <v>13</v>
-      </c>
-      <c r="D143">
-        <v>300</v>
-      </c>
-      <c r="E143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>990014</v>
-      </c>
-      <c r="B144">
-        <v>99</v>
-      </c>
-      <c r="C144">
-        <v>14</v>
-      </c>
-      <c r="D144">
-        <v>300</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>990015</v>
-      </c>
-      <c r="B145">
-        <v>99</v>
-      </c>
-      <c r="C145">
-        <v>15</v>
-      </c>
-      <c r="D145">
-        <v>300</v>
-      </c>
-      <c r="E145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>990016</v>
-      </c>
-      <c r="B146">
-        <v>99</v>
-      </c>
-      <c r="C146">
-        <v>16</v>
-      </c>
-      <c r="D146">
-        <v>300</v>
-      </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>990017</v>
-      </c>
-      <c r="B147">
-        <v>99</v>
-      </c>
-      <c r="C147">
-        <v>17</v>
-      </c>
-      <c r="D147">
-        <v>300</v>
-      </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>990018</v>
-      </c>
-      <c r="B148">
-        <v>99</v>
-      </c>
-      <c r="C148">
-        <v>18</v>
-      </c>
-      <c r="D148">
-        <v>300</v>
-      </c>
-      <c r="E148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>990019</v>
-      </c>
-      <c r="B149">
-        <v>99</v>
-      </c>
-      <c r="C149">
-        <v>19</v>
-      </c>
-      <c r="D149">
-        <v>300</v>
-      </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>990020</v>
-      </c>
-      <c r="B150">
-        <v>99</v>
-      </c>
-      <c r="C150">
-        <v>20</v>
-      </c>
-      <c r="D150">
-        <v>300</v>
-      </c>
-      <c r="E150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>990021</v>
-      </c>
-      <c r="B151">
-        <v>99</v>
-      </c>
-      <c r="C151">
-        <v>21</v>
-      </c>
-      <c r="D151">
-        <v>300</v>
-      </c>
-      <c r="E151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>990022</v>
-      </c>
-      <c r="B152">
-        <v>99</v>
-      </c>
-      <c r="C152">
-        <v>22</v>
-      </c>
-      <c r="D152">
-        <v>300</v>
-      </c>
-      <c r="E152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>990023</v>
-      </c>
-      <c r="B153">
-        <v>99</v>
-      </c>
-      <c r="C153">
-        <v>23</v>
-      </c>
-      <c r="D153">
-        <v>300</v>
-      </c>
-      <c r="E153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>990024</v>
-      </c>
-      <c r="B154">
-        <v>99</v>
-      </c>
-      <c r="C154">
-        <v>24</v>
-      </c>
-      <c r="D154">
-        <v>300</v>
-      </c>
-      <c r="E154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>990025</v>
-      </c>
-      <c r="B155">
-        <v>99</v>
-      </c>
-      <c r="C155">
-        <v>25</v>
-      </c>
-      <c r="D155">
-        <v>300</v>
-      </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>990026</v>
-      </c>
-      <c r="B156">
-        <v>99</v>
-      </c>
-      <c r="C156">
-        <v>26</v>
-      </c>
-      <c r="D156">
-        <v>300</v>
-      </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>990027</v>
-      </c>
-      <c r="B157">
-        <v>99</v>
-      </c>
-      <c r="C157">
-        <v>27</v>
-      </c>
-      <c r="D157">
-        <v>300</v>
-      </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>990028</v>
-      </c>
-      <c r="B158">
-        <v>99</v>
-      </c>
-      <c r="C158">
-        <v>28</v>
-      </c>
-      <c r="D158">
-        <v>300</v>
-      </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>990029</v>
-      </c>
-      <c r="B159">
-        <v>99</v>
-      </c>
-      <c r="C159">
-        <v>29</v>
-      </c>
-      <c r="D159">
-        <v>300</v>
-      </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>990030</v>
-      </c>
-      <c r="B160">
-        <v>99</v>
-      </c>
-      <c r="C160">
-        <v>30</v>
-      </c>
-      <c r="D160">
-        <v>300</v>
-      </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>990031</v>
-      </c>
-      <c r="B161">
-        <v>99</v>
-      </c>
-      <c r="C161">
-        <v>31</v>
-      </c>
-      <c r="D161">
-        <v>300</v>
-      </c>
-      <c r="E161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>990032</v>
-      </c>
-      <c r="B162">
-        <v>99</v>
-      </c>
-      <c r="C162">
-        <v>32</v>
-      </c>
-      <c r="D162">
-        <v>300</v>
-      </c>
-      <c r="E162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>990033</v>
-      </c>
-      <c r="B163">
-        <v>99</v>
-      </c>
-      <c r="C163">
-        <v>33</v>
-      </c>
-      <c r="D163">
-        <v>300</v>
-      </c>
-      <c r="E163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>990034</v>
-      </c>
-      <c r="B164">
-        <v>99</v>
-      </c>
-      <c r="C164">
-        <v>34</v>
-      </c>
-      <c r="D164">
-        <v>300</v>
-      </c>
-      <c r="E164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>990035</v>
-      </c>
-      <c r="B165">
-        <v>99</v>
-      </c>
-      <c r="C165">
-        <v>35</v>
-      </c>
-      <c r="D165">
-        <v>300</v>
-      </c>
-      <c r="E165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>990036</v>
-      </c>
-      <c r="B166">
-        <v>99</v>
-      </c>
-      <c r="C166">
-        <v>36</v>
-      </c>
-      <c r="D166">
-        <v>300</v>
-      </c>
-      <c r="E166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>990037</v>
-      </c>
-      <c r="B167">
-        <v>99</v>
-      </c>
-      <c r="C167">
-        <v>37</v>
-      </c>
-      <c r="D167">
-        <v>300</v>
-      </c>
-      <c r="E167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>990038</v>
-      </c>
-      <c r="B168">
-        <v>99</v>
-      </c>
-      <c r="C168">
-        <v>38</v>
-      </c>
-      <c r="D168">
-        <v>300</v>
-      </c>
-      <c r="E168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>990039</v>
-      </c>
-      <c r="B169">
-        <v>99</v>
-      </c>
-      <c r="C169">
-        <v>39</v>
-      </c>
-      <c r="D169">
-        <v>300</v>
-      </c>
-      <c r="E169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>990040</v>
-      </c>
-      <c r="B170">
-        <v>99</v>
-      </c>
-      <c r="C170">
-        <v>40</v>
-      </c>
-      <c r="D170">
-        <v>300</v>
-      </c>
-      <c r="E170">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>990041</v>
-      </c>
-      <c r="B171">
-        <v>99</v>
-      </c>
-      <c r="C171">
-        <v>41</v>
-      </c>
-      <c r="D171">
-        <v>300</v>
-      </c>
-      <c r="E171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>990042</v>
-      </c>
-      <c r="B172">
-        <v>99</v>
-      </c>
-      <c r="C172">
-        <v>42</v>
-      </c>
-      <c r="D172">
-        <v>300</v>
-      </c>
-      <c r="E172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>990043</v>
-      </c>
-      <c r="B173">
-        <v>99</v>
-      </c>
-      <c r="C173">
-        <v>43</v>
-      </c>
-      <c r="D173">
-        <v>300</v>
-      </c>
-      <c r="E173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>990044</v>
-      </c>
-      <c r="B174">
-        <v>99</v>
-      </c>
-      <c r="C174">
-        <v>44</v>
-      </c>
-      <c r="D174">
-        <v>300</v>
-      </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>990045</v>
-      </c>
-      <c r="B175">
-        <v>99</v>
-      </c>
-      <c r="C175">
-        <v>45</v>
-      </c>
-      <c r="D175">
-        <v>300</v>
-      </c>
-      <c r="E175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>990046</v>
-      </c>
-      <c r="B176">
-        <v>99</v>
-      </c>
-      <c r="C176">
-        <v>46</v>
-      </c>
-      <c r="D176">
-        <v>300</v>
-      </c>
-      <c r="E176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>990047</v>
-      </c>
-      <c r="B177">
-        <v>99</v>
-      </c>
-      <c r="C177">
-        <v>47</v>
-      </c>
-      <c r="D177">
-        <v>300</v>
-      </c>
-      <c r="E177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>990048</v>
-      </c>
-      <c r="B178">
-        <v>99</v>
-      </c>
-      <c r="C178">
-        <v>48</v>
-      </c>
-      <c r="D178">
-        <v>300</v>
-      </c>
-      <c r="E178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>990049</v>
-      </c>
-      <c r="B179">
-        <v>99</v>
-      </c>
-      <c r="C179">
-        <v>49</v>
-      </c>
-      <c r="D179">
-        <v>300</v>
-      </c>
-      <c r="E179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>990050</v>
-      </c>
-      <c r="B180">
-        <v>99</v>
-      </c>
-      <c r="C180">
-        <v>50</v>
-      </c>
-      <c r="D180">
-        <v>300</v>
-      </c>
-      <c r="E180">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>990051</v>
-      </c>
-      <c r="B181">
-        <v>99</v>
-      </c>
-      <c r="C181">
-        <v>51</v>
-      </c>
-      <c r="D181">
-        <v>300</v>
-      </c>
-      <c r="E181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>990052</v>
-      </c>
-      <c r="B182">
-        <v>99</v>
-      </c>
-      <c r="C182">
-        <v>52</v>
-      </c>
-      <c r="D182">
-        <v>300</v>
-      </c>
-      <c r="E182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>990053</v>
-      </c>
-      <c r="B183">
-        <v>99</v>
-      </c>
-      <c r="C183">
-        <v>53</v>
-      </c>
-      <c r="D183">
-        <v>300</v>
-      </c>
-      <c r="E183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>990054</v>
-      </c>
-      <c r="B184">
-        <v>99</v>
-      </c>
-      <c r="C184">
-        <v>54</v>
-      </c>
-      <c r="D184">
-        <v>300</v>
-      </c>
-      <c r="E184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>990055</v>
-      </c>
-      <c r="B185">
-        <v>99</v>
-      </c>
-      <c r="C185">
-        <v>55</v>
-      </c>
-      <c r="D185">
-        <v>300</v>
-      </c>
-      <c r="E185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>990056</v>
-      </c>
-      <c r="B186">
-        <v>99</v>
-      </c>
-      <c r="C186">
-        <v>56</v>
-      </c>
-      <c r="D186">
-        <v>300</v>
-      </c>
-      <c r="E186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>990057</v>
-      </c>
-      <c r="B187">
-        <v>99</v>
-      </c>
-      <c r="C187">
-        <v>57</v>
-      </c>
-      <c r="D187">
-        <v>300</v>
-      </c>
-      <c r="E187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>990058</v>
-      </c>
-      <c r="B188">
-        <v>99</v>
-      </c>
-      <c r="C188">
-        <v>58</v>
-      </c>
-      <c r="D188">
-        <v>300</v>
-      </c>
-      <c r="E188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>990059</v>
-      </c>
-      <c r="B189">
-        <v>99</v>
-      </c>
-      <c r="C189">
-        <v>59</v>
-      </c>
-      <c r="D189">
-        <v>300</v>
-      </c>
-      <c r="E189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>990060</v>
-      </c>
-      <c r="B190">
-        <v>99</v>
-      </c>
-      <c r="C190">
-        <v>60</v>
-      </c>
-      <c r="D190">
-        <v>300</v>
-      </c>
-      <c r="E190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A191">
-        <v>990061</v>
-      </c>
-      <c r="B191">
-        <v>99</v>
-      </c>
-      <c r="C191">
-        <v>61</v>
-      </c>
-      <c r="D191">
-        <v>300</v>
-      </c>
-      <c r="E191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>990062</v>
-      </c>
-      <c r="B192">
-        <v>99</v>
-      </c>
-      <c r="C192">
-        <v>62</v>
-      </c>
-      <c r="D192">
-        <v>300</v>
-      </c>
-      <c r="E192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>990063</v>
-      </c>
-      <c r="B193">
-        <v>99</v>
-      </c>
-      <c r="C193">
-        <v>63</v>
-      </c>
-      <c r="D193">
-        <v>300</v>
-      </c>
-      <c r="E193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>990064</v>
-      </c>
-      <c r="B194">
-        <v>99</v>
-      </c>
-      <c r="C194">
-        <v>64</v>
-      </c>
-      <c r="D194">
-        <v>300</v>
-      </c>
-      <c r="E194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195">
-        <v>990065</v>
-      </c>
-      <c r="B195">
-        <v>99</v>
-      </c>
-      <c r="C195">
-        <v>65</v>
-      </c>
-      <c r="D195">
-        <v>300</v>
-      </c>
-      <c r="E195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196">
-        <v>990066</v>
-      </c>
-      <c r="B196">
-        <v>99</v>
-      </c>
-      <c r="C196">
-        <v>66</v>
-      </c>
-      <c r="D196">
-        <v>300</v>
-      </c>
-      <c r="E196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A197">
-        <v>990067</v>
-      </c>
-      <c r="B197">
-        <v>99</v>
-      </c>
-      <c r="C197">
-        <v>67</v>
-      </c>
-      <c r="D197">
-        <v>300</v>
-      </c>
-      <c r="E197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198">
-        <v>990068</v>
-      </c>
-      <c r="B198">
-        <v>99</v>
-      </c>
-      <c r="C198">
-        <v>68</v>
-      </c>
-      <c r="D198">
-        <v>300</v>
-      </c>
-      <c r="E198">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199">
-        <v>990069</v>
-      </c>
-      <c r="B199">
-        <v>99</v>
-      </c>
-      <c r="C199">
-        <v>69</v>
-      </c>
-      <c r="D199">
-        <v>300</v>
-      </c>
-      <c r="E199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200">
-        <v>990070</v>
-      </c>
-      <c r="B200">
-        <v>99</v>
-      </c>
-      <c r="C200">
-        <v>70</v>
-      </c>
-      <c r="D200">
-        <v>300</v>
-      </c>
-      <c r="E200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>990071</v>
-      </c>
-      <c r="B201">
-        <v>99</v>
-      </c>
-      <c r="C201">
-        <v>71</v>
-      </c>
-      <c r="D201">
-        <v>300</v>
-      </c>
-      <c r="E201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>990072</v>
-      </c>
-      <c r="B202">
-        <v>99</v>
-      </c>
-      <c r="C202">
-        <v>72</v>
-      </c>
-      <c r="D202">
-        <v>300</v>
-      </c>
-      <c r="E202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>990073</v>
-      </c>
-      <c r="B203">
-        <v>99</v>
-      </c>
-      <c r="C203">
-        <v>73</v>
-      </c>
-      <c r="D203">
-        <v>300</v>
-      </c>
-      <c r="E203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>990074</v>
-      </c>
-      <c r="B204">
-        <v>99</v>
-      </c>
-      <c r="C204">
-        <v>74</v>
-      </c>
-      <c r="D204">
-        <v>300</v>
-      </c>
-      <c r="E204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>990075</v>
-      </c>
-      <c r="B205">
-        <v>99</v>
-      </c>
-      <c r="C205">
-        <v>75</v>
-      </c>
-      <c r="D205">
-        <v>300</v>
-      </c>
-      <c r="E205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>990076</v>
-      </c>
-      <c r="B206">
-        <v>99</v>
-      </c>
-      <c r="C206">
-        <v>76</v>
-      </c>
-      <c r="D206">
-        <v>300</v>
-      </c>
-      <c r="E206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>990077</v>
-      </c>
-      <c r="B207">
-        <v>99</v>
-      </c>
-      <c r="C207">
-        <v>77</v>
-      </c>
-      <c r="D207">
-        <v>300</v>
-      </c>
-      <c r="E207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208">
-        <v>990078</v>
-      </c>
-      <c r="B208">
-        <v>99</v>
-      </c>
-      <c r="C208">
-        <v>78</v>
-      </c>
-      <c r="D208">
-        <v>300</v>
-      </c>
-      <c r="E208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>990079</v>
-      </c>
-      <c r="B209">
-        <v>99</v>
-      </c>
-      <c r="C209">
-        <v>79</v>
-      </c>
-      <c r="D209">
-        <v>300</v>
-      </c>
-      <c r="E209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A210">
-        <v>990080</v>
-      </c>
-      <c r="B210">
-        <v>99</v>
-      </c>
-      <c r="C210">
-        <v>80</v>
-      </c>
-      <c r="D210">
-        <v>300</v>
-      </c>
-      <c r="E210">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>990081</v>
-      </c>
-      <c r="B211">
-        <v>99</v>
-      </c>
-      <c r="C211">
-        <v>81</v>
-      </c>
-      <c r="D211">
-        <v>300</v>
-      </c>
-      <c r="E211">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>990082</v>
-      </c>
-      <c r="B212">
-        <v>99</v>
-      </c>
-      <c r="C212">
-        <v>82</v>
-      </c>
-      <c r="D212">
-        <v>300</v>
-      </c>
-      <c r="E212">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>990083</v>
-      </c>
-      <c r="B213">
-        <v>99</v>
-      </c>
-      <c r="C213">
-        <v>83</v>
-      </c>
-      <c r="D213">
-        <v>300</v>
-      </c>
-      <c r="E213">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>990084</v>
-      </c>
-      <c r="B214">
-        <v>99</v>
-      </c>
-      <c r="C214">
-        <v>84</v>
-      </c>
-      <c r="D214">
-        <v>300</v>
-      </c>
-      <c r="E214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>990085</v>
-      </c>
-      <c r="B215">
-        <v>99</v>
-      </c>
-      <c r="C215">
-        <v>85</v>
-      </c>
-      <c r="D215">
-        <v>300</v>
-      </c>
-      <c r="E215">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>990086</v>
-      </c>
-      <c r="B216">
-        <v>99</v>
-      </c>
-      <c r="C216">
-        <v>86</v>
-      </c>
-      <c r="D216">
-        <v>300</v>
-      </c>
-      <c r="E216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>990087</v>
-      </c>
-      <c r="B217">
-        <v>99</v>
-      </c>
-      <c r="C217">
-        <v>87</v>
-      </c>
-      <c r="D217">
-        <v>300</v>
-      </c>
-      <c r="E217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>990088</v>
-      </c>
-      <c r="B218">
-        <v>99</v>
-      </c>
-      <c r="C218">
-        <v>88</v>
-      </c>
-      <c r="D218">
-        <v>300</v>
-      </c>
-      <c r="E218">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A219">
-        <v>990089</v>
-      </c>
-      <c r="B219">
-        <v>99</v>
-      </c>
-      <c r="C219">
-        <v>89</v>
-      </c>
-      <c r="D219">
-        <v>300</v>
-      </c>
-      <c r="E219">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A220">
-        <v>990090</v>
-      </c>
-      <c r="B220">
-        <v>99</v>
-      </c>
-      <c r="C220">
-        <v>90</v>
-      </c>
-      <c r="D220">
-        <v>300</v>
-      </c>
-      <c r="E220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>990091</v>
-      </c>
-      <c r="B221">
-        <v>99</v>
-      </c>
-      <c r="C221">
-        <v>91</v>
-      </c>
-      <c r="D221">
-        <v>300</v>
-      </c>
-      <c r="E221">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>990092</v>
-      </c>
-      <c r="B222">
-        <v>99</v>
-      </c>
-      <c r="C222">
-        <v>92</v>
-      </c>
-      <c r="D222">
-        <v>300</v>
-      </c>
-      <c r="E222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A223">
-        <v>990093</v>
-      </c>
-      <c r="B223">
-        <v>99</v>
-      </c>
-      <c r="C223">
-        <v>93</v>
-      </c>
-      <c r="D223">
-        <v>300</v>
-      </c>
-      <c r="E223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>990094</v>
-      </c>
-      <c r="B224">
-        <v>99</v>
-      </c>
-      <c r="C224">
-        <v>94</v>
-      </c>
-      <c r="D224">
-        <v>300</v>
-      </c>
-      <c r="E224">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225">
-        <v>990095</v>
-      </c>
-      <c r="B225">
-        <v>99</v>
-      </c>
-      <c r="C225">
-        <v>95</v>
-      </c>
-      <c r="D225">
-        <v>300</v>
-      </c>
-      <c r="E225">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>990096</v>
-      </c>
-      <c r="B226">
-        <v>99</v>
-      </c>
-      <c r="C226">
-        <v>96</v>
-      </c>
-      <c r="D226">
-        <v>300</v>
-      </c>
-      <c r="E226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227">
-        <v>990097</v>
-      </c>
-      <c r="B227">
-        <v>99</v>
-      </c>
-      <c r="C227">
-        <v>97</v>
-      </c>
-      <c r="D227">
-        <v>300</v>
-      </c>
-      <c r="E227">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>990098</v>
-      </c>
-      <c r="B228">
-        <v>99</v>
-      </c>
-      <c r="C228">
-        <v>98</v>
-      </c>
-      <c r="D228">
-        <v>300</v>
-      </c>
-      <c r="E228">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229">
-        <v>990099</v>
-      </c>
-      <c r="B229">
-        <v>99</v>
-      </c>
-      <c r="C229">
-        <v>99</v>
-      </c>
-      <c r="D229">
-        <v>300</v>
-      </c>
-      <c r="E229">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230">
-        <v>990100</v>
-      </c>
-      <c r="B230">
-        <v>99</v>
-      </c>
-      <c r="C230">
-        <v>100</v>
-      </c>
-      <c r="D230">
-        <v>300</v>
-      </c>
-      <c r="E230">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C40D998-A502-49D8-880E-0F22E1D9E7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632DBC8E-69DD-4096-BAA8-2469652CB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="D138">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E139">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E140EC0F-4BAB-44CD-AC9B-CA3B722389CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0B137-3209-4D3D-85A5-B38B3CD860AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -3061,13 +3061,13 @@
         <v>2</v>
       </c>
       <c r="D132" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
       </c>
       <c r="F132" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -3081,13 +3081,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
       </c>
       <c r="F133" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -3101,13 +3101,13 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
       </c>
       <c r="F134" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -3121,13 +3121,13 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
       </c>
       <c r="F135" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -3141,13 +3141,13 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
       </c>
       <c r="F136" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -3161,13 +3161,13 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
       </c>
       <c r="F137" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -3181,13 +3181,13 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
       </c>
       <c r="F138" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -3201,13 +3201,13 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
       </c>
       <c r="F139" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0B137-3209-4D3D-85A5-B38B3CD860AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B684E0-C9E7-48A1-A70F-AFC10197BEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$219</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3027,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -3061,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B684E0-C9E7-48A1-A70F-AFC10197BEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A7E336-8B4E-4129-B28F-891F6BDBD340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
